--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/phi-4/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/phi-4/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.671875</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4397163120567376</v>
+        <v>0.3591549295774648</v>
       </c>
       <c r="D2">
-        <v>0.6475409836065574</v>
+        <v>0.7520661157024794</v>
       </c>
       <c r="E2">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F2">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="G2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
